--- a/deliverables/POC_420_Songbook_Phase4_Commitment.xlsx
+++ b/deliverables/POC_420_Songbook_Phase4_Commitment.xlsx
@@ -868,7 +868,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CEN Research-Partner Meeting  |  2026-04-17  |  Version 1.0  |  Date: 2026-04-15</t>
+          <t>CEN Research-Partner Meeting  |  2026-04-17  |  Version 1.1  |  Date: 2026-04-16</t>
         </is>
       </c>
     </row>
